--- a/examples/sample.xlsx
+++ b/examples/sample.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>本地化键</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +486,11 @@
           <t>LocKey</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -513,6 +523,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +558,11 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Loc 表外键</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>每行的人类可读注释</t>
         </is>
       </c>
     </row>
@@ -573,6 +593,7 @@
           <t>ITEM_10001_NAME</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -601,6 +622,7 @@
           <t>ITEM_10002_NAME</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -629,6 +651,7 @@
           <t>ITEM_10003_NAME</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -657,6 +680,7 @@
           <t>ITEM_10004_NAME</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -685,6 +709,7 @@
           <t>ITEM_10005_NAME</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
